--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484095_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484095_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3379</v>
+        <v>1.3939</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7834</v>
+        <v>5.0918</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.4455</v>
+        <v>-3.698</v>
       </c>
       <c r="G2" t="n">
         <v>-3.5245</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2511</v>
+        <v>-0.6929</v>
       </c>
       <c r="T2" t="n">
-        <v>0.754</v>
+        <v>0.0625</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5029</v>
+        <v>-0.7554</v>
       </c>
       <c r="V2" t="n">
         <v>4.2226</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3428</v>
+        <v>0.349</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1364</v>
+        <v>-0.0741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4792</v>
+        <v>0.4231</v>
       </c>
       <c r="G3" t="n">
         <v>0.9413</v>
@@ -688,13 +688,13 @@
         <v>0.1984</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1224</v>
+        <v>-0.1162</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1247</v>
+        <v>-0.0623</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0022</v>
+        <v>-0.0539</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6745</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2787</v>
+        <v>-0.2025</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9066</v>
+        <v>1.2641</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1853</v>
+        <v>-1.4667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2735</v>
+        <v>-1.4033</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.618</v>
+        <v>-4.1278</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8915</v>
+        <v>2.7245</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3884</v>
+        <v>1.1179</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6197</v>
+        <v>-1.8591</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0081</v>
+        <v>2.9771</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1148</v>
+        <v>-2.5213</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9983</v>
+        <v>-2.2687</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1165</v>
+        <v>-0.2526</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6036</v>
+        <v>-1.1166</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1928</v>
+        <v>-0.4534</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7964</v>
+        <v>-0.6632</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9405</v>
+        <v>0.532</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6745</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X4" t="n">
         <v>-0.266</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3081</v>
+        <v>-0.2801</v>
       </c>
       <c r="E5" t="n">
         <v>-0.4564</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1483</v>
+        <v>0.1763</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9272</v>
@@ -844,13 +844,13 @@
         <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0436</v>
+        <v>-0.0156</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6107</v>
+        <v>-0.2801</v>
       </c>
       <c r="E6" t="n">
-        <v>0.856</v>
+        <v>0.7649</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4667</v>
+        <v>-1.045</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4033</v>
+        <v>0.2735</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.1278</v>
+        <v>-1.618</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7245</v>
+        <v>1.8915</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1179</v>
+        <v>1.3884</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.8591</v>
+        <v>-0.6197</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9771</v>
+        <v>2.0081</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5213</v>
+        <v>-1.1148</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2687</v>
+        <v>-0.9983</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2526</v>
+        <v>-0.1165</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5247</v>
+        <v>-0.6051</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8615</v>
+        <v>0.0511</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6632</v>
+        <v>-0.6561</v>
       </c>
       <c r="V6" t="n">
-        <v>0.532</v>
+        <v>-0.9405</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.6745</v>
       </c>
       <c r="X6" t="n">
         <v>-0.266</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3892</v>
+        <v>-1.3115</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5211</v>
+        <v>2.9915</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9102</v>
+        <v>-4.303</v>
       </c>
       <c r="G7" t="n">
         <v>-2.5398</v>
@@ -1000,13 +1000,13 @@
         <v>2.9758</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1631</v>
+        <v>-1.0854</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8047</v>
+        <v>-0.3343</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3584</v>
+        <v>-0.7512</v>
       </c>
       <c r="V7" t="n">
         <v>0.7267</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0703</v>
+        <v>-3.0539</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0641</v>
+        <v>-1.1038</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0062</v>
+        <v>-1.9501</v>
       </c>
       <c r="G8" t="n">
         <v>-3.8717</v>
@@ -1078,13 +1078,13 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.853</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1418</v>
+        <v>0.1021</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0113</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>1.4724</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7566</v>
+        <v>-3.2096</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0289</v>
+        <v>-0.7625</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7277</v>
+        <v>-2.4472</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0165</v>
@@ -1156,13 +1156,13 @@
         <v>2.7774</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7401</v>
+        <v>-1.1931</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6177</v>
+        <v>-0.3513</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1224</v>
+        <v>-0.8418</v>
       </c>
       <c r="V9" t="n">
         <v>0.6032</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.784</v>
+        <v>-4.3047</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7873</v>
+        <v>-1.5606</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9967</v>
+        <v>-2.7442</v>
       </c>
       <c r="G10" t="n">
         <v>-6.1418</v>
@@ -1234,13 +1234,13 @@
         <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4357</v>
+        <v>-0.9565</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.306</v>
+        <v>-0.0793</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1297</v>
+        <v>-0.8772</v>
       </c>
       <c r="V10" t="n">
         <v>1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.4369</v>
+        <v>-8.4307</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2353</v>
+        <v>-4.173</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2016</v>
+        <v>-4.2577</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6643</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2017</v>
+        <v>-0.1955</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1872</v>
+        <v>0.2495</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3889</v>
+        <v>-0.445</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.9538</v>
+        <v>-19.3302</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3587</v>
+        <v>1.9819</v>
       </c>
       <c r="F12" t="n">
-        <v>-21.3124</v>
+        <v>-21.3125</v>
       </c>
       <c r="G12" t="n">
         <v>-24.8743</v>
@@ -1390,13 +1390,13 @@
         <v>16.8628</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.453299999999999</v>
+        <v>-6.8299</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5011</v>
+        <v>-0.8776999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.952299999999999</v>
+        <v>-5.952100000000001</v>
       </c>
       <c r="V12" t="n">
         <v>7.4144</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.675</v>
+        <v>6.3488</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9604</v>
+        <v>5.3377</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7146</v>
+        <v>1.0111</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3305</v>
+        <v>4.9323</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3125</v>
+        <v>0.6401</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.982</v>
+        <v>4.2922</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7684</v>
+        <v>4.7409</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6881</v>
+        <v>0.2027</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0803</v>
+        <v>4.5383</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4379</v>
+        <v>0.1914</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6244</v>
+        <v>0.4374</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0623</v>
+        <v>-0.2461</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1741</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7935</v>
+        <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7729</v>
+        <v>0.6943</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5564</v>
+        <v>0.4535</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2165</v>
+        <v>0.2408</v>
       </c>
       <c r="V13" t="n">
-        <v>1.9522</v>
+        <v>-0.0713</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8097</v>
+        <v>1.1352</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1425</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5378</v>
+        <v>5.3588</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8059</v>
+        <v>4.532</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7319</v>
+        <v>0.8268</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3047</v>
+        <v>4.3305</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1622</v>
+        <v>5.3125</v>
       </c>
       <c r="I14" t="n">
+        <v>-0.982</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.7684</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.6881</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.4379</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.0623</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-2.3806</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-3.1741</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.4567</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.9522</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.8097</v>
+      </c>
+      <c r="X14" t="n">
         <v>0.1425</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.6836</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.8803</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.8032</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.3788</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.2818</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-0.6607</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.8922</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.1224</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.2302</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.349</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.349</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.014</v>
+        <v>5.1076</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4195</v>
+        <v>3.2958</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5945</v>
+        <v>1.8118</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9323</v>
+        <v>2.3047</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6401</v>
+        <v>2.1622</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2922</v>
+        <v>0.1425</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7409</v>
+        <v>2.6836</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2027</v>
+        <v>1.8803</v>
       </c>
       <c r="L15" t="n">
-        <v>4.5383</v>
+        <v>0.8032</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1914</v>
+        <v>-0.3788</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4374</v>
+        <v>0.2818</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2461</v>
+        <v>-0.6607</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6405</v>
+        <v>0.462</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4647</v>
+        <v>0.6122</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1758</v>
+        <v>-0.1503</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0713</v>
+        <v>1.349</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1352</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2065</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3629</v>
+        <v>4.3383</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9963</v>
+        <v>4.2003</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3666</v>
+        <v>0.1379</v>
       </c>
       <c r="G16" t="n">
         <v>3.0919</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2872</v>
+        <v>1.2626</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3912</v>
+        <v>0.5952</v>
       </c>
       <c r="U16" t="n">
-        <v>0.896</v>
+        <v>0.6673</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2065</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1655</v>
+        <v>2.9054</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4353</v>
+        <v>2.2313</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7302</v>
+        <v>0.6741</v>
       </c>
       <c r="G17" t="n">
         <v>2.4718</v>
@@ -1780,13 +1780,13 @@
         <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8922</v>
+        <v>0.632</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6292</v>
+        <v>0.4251</v>
       </c>
       <c r="U17" t="n">
-        <v>0.263</v>
+        <v>0.2069</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.744</v>
+        <v>2.7517</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2416</v>
+        <v>3.4457</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4976</v>
+        <v>-0.694</v>
       </c>
       <c r="G18" t="n">
         <v>5.0483</v>
@@ -1858,13 +1858,13 @@
         <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2747</v>
+        <v>1.2824</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3288</v>
+        <v>0.5329</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9459</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6032</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0414</v>
+        <v>-0.013</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6791</v>
+        <v>-0.7811</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7205</v>
+        <v>0.7681</v>
       </c>
       <c r="G19" t="n">
         <v>0.5639</v>
@@ -1936,13 +1936,13 @@
         <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4738</v>
+        <v>0.4194</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4025</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0307</v>
+        <v>0.017</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7979000000000001</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>F. LOPEZ BARCELO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1962</v>
+        <v>-0.6364</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8673</v>
+        <v>1.9307</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3289</v>
+        <v>-2.5671</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4437</v>
+        <v>3.5332</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1963</v>
+        <v>2.1872</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.64</v>
+        <v>1.346</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.06809999999999999</v>
+        <v>3.7104</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4489</v>
+        <v>1.9758</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.517</v>
+        <v>1.7346</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3756</v>
+        <v>-0.1772</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2525</v>
+        <v>0.2114</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.123</v>
+        <v>-0.3886</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2556</v>
+        <v>-0.102</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1928</v>
+        <v>0.2041</v>
       </c>
       <c r="U20" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.3061</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. LOPEZ BARCELO</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.439</v>
+        <v>-0.9062</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6246</v>
+        <v>-0.7653</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0636</v>
+        <v>-0.141</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5332</v>
+        <v>-0.4437</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1872</v>
+        <v>0.1963</v>
       </c>
       <c r="I21" t="n">
-        <v>1.346</v>
+        <v>-0.64</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7104</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9758</v>
+        <v>0.4489</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7346</v>
+        <v>-0.517</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1772</v>
+        <v>-0.3756</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2114</v>
+        <v>-0.2525</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3886</v>
+        <v>-0.123</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9046</v>
+        <v>0.5456</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.102</v>
+        <v>0.2948</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8026</v>
+        <v>0.2507</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.6789</v>
+        <v>-1.2065</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6789</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7507</v>
+        <v>-1.5925</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.7215</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3701</v>
+        <v>-2.314</v>
       </c>
       <c r="G22" t="n">
         <v>0.1361</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>1.205</v>
+        <v>1.3632</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6519</v>
+        <v>0.7539</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5531</v>
+        <v>0.6092</v>
       </c>
       <c r="V22" t="n">
         <v>-3.8854</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2011</v>
+        <v>-2.3483</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2443</v>
+        <v>-2.8362</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0432</v>
+        <v>0.4878</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0947</v>
@@ -2248,13 +2248,13 @@
         <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.055</v>
+        <v>0.7978</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1418</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1968</v>
+        <v>0.2479</v>
       </c>
       <c r="V23" t="n">
         <v>-0.266</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>19.9536</v>
+        <v>21.3142</v>
       </c>
       <c r="E24" t="n">
         <v>21.3124</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3587</v>
+        <v>0.001500000000000501</v>
       </c>
       <c r="G24" t="n">
         <v>24.8743</v>
@@ -2326,13 +2326,13 @@
         <v>11.903</v>
       </c>
       <c r="S24" t="n">
-        <v>7.4535</v>
+        <v>8.814000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>5.9523</v>
+        <v>5.952100000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5012</v>
+        <v>2.8616</v>
       </c>
       <c r="V24" t="n">
         <v>-7.4145</v>
